--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Dokumentation der Substanz eines Inhaltsstoffes eines Arzneimittels, sofern es nicht kodiert vorliegt.</t>
+    <t>Dokumentation der Substanz eines Inhaltsstoffes eines Arzneimittels, sofern es nicht kodiert vorliegt.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
